--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1237,10 +1237,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -6599,7 +6596,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>388</v>
       </c>
@@ -6618,7 +6615,7 @@
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6662,13 +6659,11 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y39" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Y39" s="2"/>
+      <c r="Z39" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6704,27 +6699,27 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6750,16 +6745,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6787,11 +6782,11 @@
         <v>207</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6808,7 +6803,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6829,10 +6824,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6843,10 +6838,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6869,16 +6864,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6928,7 +6923,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6946,27 +6941,27 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6989,16 +6984,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7048,7 +7043,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7066,27 +7061,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7109,19 +7104,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7170,7 +7165,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7182,19 +7177,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7205,10 +7200,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7323,10 +7318,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7443,14 +7438,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7472,10 +7467,10 @@
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
@@ -7530,7 +7525,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7565,10 +7560,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7591,13 +7586,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7648,7 +7643,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7657,7 +7652,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7669,10 +7664,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7683,10 +7678,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7709,13 +7704,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7766,7 +7761,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7775,7 +7770,7 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7787,10 +7782,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7801,10 +7796,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7830,16 +7825,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7867,11 +7862,11 @@
         <v>117</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7888,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7906,10 +7901,10 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>378</v>
@@ -7923,10 +7918,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7952,16 +7947,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7989,11 +7984,11 @@
         <v>207</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8010,7 +8005,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8028,10 +8023,10 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>378</v>
@@ -8045,10 +8040,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8071,17 +8066,17 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8130,7 +8125,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8154,7 +8149,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8165,10 +8160,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8194,10 +8189,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8248,7 +8243,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8269,10 +8264,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8283,10 +8278,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8309,16 +8304,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8368,7 +8363,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8389,10 +8384,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8403,10 +8398,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8429,16 +8424,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8488,7 +8483,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8509,10 +8504,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8523,10 +8518,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8549,19 +8544,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8610,7 +8605,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8631,10 +8626,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8645,10 +8640,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8763,10 +8758,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8883,14 +8878,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8912,10 +8907,10 @@
         <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>142</v>
@@ -8970,7 +8965,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9005,10 +9000,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9034,13 +9029,13 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>206</v>
@@ -9092,7 +9087,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>93</v>
@@ -9110,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>212</v>
@@ -9127,10 +9122,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9153,16 +9148,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>351</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>353</v>
@@ -9214,7 +9209,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9232,7 +9227,7 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>356</v>
@@ -9249,10 +9244,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9278,13 +9273,13 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>363</v>
@@ -9336,7 +9331,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9371,10 +9366,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9400,7 +9395,7 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>372</v>
@@ -9437,11 +9432,11 @@
         <v>364</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9458,7 +9453,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9493,10 +9488,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9522,16 +9517,16 @@
         <v>83</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="N63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9580,7 +9575,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9601,10 +9596,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-pain-score-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
